--- a/テスト用_本葬受付台帳.xlsx
+++ b/テスト用_本葬受付台帳.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受付台帳" sheetId="1" r:id="R8d8c62edd80c4b39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名前ルール" sheetId="2" r:id="R2543e670d59b48ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名前ルール設定" sheetId="3" r:id="Re69a13b9149441c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受付台帳" sheetId="1" r:id="Rf8ce25e32b8a47f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名前ルール" sheetId="2" r:id="Rf1561ee931cb4e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名前ルール設定" sheetId="3" r:id="R7be72d5cb1bf430e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -29,6 +29,12 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
@@ -57,7 +63,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -88,6 +94,23 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -414,6 +437,9 @@
     <x:col min="31" max="31" width="15" customWidth="1"/>
     <x:col min="32" max="32" width="15" customWidth="1"/>
     <x:col min="33" max="33" width="15" customWidth="1"/>
+    <x:col min="34" max="34" width="12" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="24" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -582,6 +608,15 @@
           <x:t xml:space="preserve">マイナス小計</x:t>
         </x:is>
       </x:c>
+      <x:c r="AH1" s="24" t="str">
+        <x:v>郵便番号</x:v>
+      </x:c>
+      <x:c r="AI1" s="24" t="str">
+        <x:v>住所（数字）</x:v>
+      </x:c>
+      <x:c r="AJ1" s="24" t="str">
+        <x:v>住所（漢数字）</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="n">
@@ -733,6 +768,13 @@
       <x:c r="AG2" t="n">
         <x:v>190000</x:v>
       </x:c>
+      <x:c r="AH2" s="13" t="str"/>
+      <x:c r="AI2" s="13" t="str">
+        <x:v>北斗市本町290</x:v>
+      </x:c>
+      <x:c r="AJ2" s="13" t="str">
+        <x:v>北斗市本町二九〇</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="n">
@@ -892,6 +934,9 @@
       <x:c r="AG3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AH3" s="13" t="str"/>
+      <x:c r="AI3" s="13" t="str"/>
+      <x:c r="AJ3" s="13" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
